--- a/CV.xlsx
+++ b/CV.xlsx
@@ -5,26 +5,26 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="11"/>
   </bookViews>
   <sheets>
-    <sheet name="Education" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Thesis" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Experience" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Grants" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="PRS" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Awards" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="Software" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="Talks" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="Teaching" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="Workshops" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="CourseDev" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="Mentoring" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="Committees" sheetId="13" state="visible" r:id="rId14"/>
-    <sheet name="Service" sheetId="14" state="visible" r:id="rId15"/>
-    <sheet name="Reviewing" sheetId="15" state="visible" r:id="rId16"/>
-    <sheet name="ProfDev" sheetId="16" state="visible" r:id="rId17"/>
-    <sheet name="Outreach" sheetId="17" state="visible" r:id="rId18"/>
+    <sheet name="Education" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Thesis" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Experience" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Grants" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="PRS" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Awards" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Software" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Talks" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Teaching" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Workshops" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="CourseDev" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Mentoring" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Committees" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Service" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Reviewing" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="ProfDev" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Outreach" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="747">
   <si>
     <t xml:space="preserve">degree</t>
   </si>
@@ -1914,7 +1914,7 @@
     <t xml:space="preserve">An Historical Analysis of Pie and Bar Chart Experiments</t>
   </si>
   <si>
-    <t xml:space="preserve">Dinuwanthi Lianage</t>
+    <t xml:space="preserve">Dinuwanthi Liyanage</t>
   </si>
   <si>
     <t xml:space="preserve">Harriet Mason</t>
@@ -1941,6 +1941,9 @@
     <t xml:space="preserve">UNL Undergraduate Research Program</t>
   </si>
   <si>
+    <t xml:space="preserve">Transferred to Southern Illinois University due to program elimination at UNL</t>
+  </si>
+  <si>
     <t xml:space="preserve">Student Name</t>
   </si>
   <si>
@@ -2202,7 +2205,7 @@
     <t xml:space="preserve">Legal Briefs and Testimony</t>
   </si>
   <si>
-    <t xml:space="preserve">Amicus Curiae Brief</t>
+    <t xml:space="preserve">Written Testimony</t>
   </si>
   <si>
     <t xml:space="preserve">Michigan</t>
@@ -2224,9 +2227,6 @@
   </si>
   <si>
     <t xml:space="preserve">People v. Martinez-Sarmiento, 23CR2638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Written Testimony</t>
   </si>
   <si>
     <t xml:space="preserve">People v. Fielder, Denver County, 23CR5433.</t>
@@ -2287,15 +2287,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="General"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-m"/>
+    <numFmt numFmtId="167" formatCode="yyyy\-mm"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-m"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2332,6 +2331,12 @@
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2376,7 +2381,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2401,11 +2406,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2415,10 +2416,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -2433,7 +2430,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2441,7 +2442,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2457,13 +2458,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2654,7 +2761,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2681,7 +2788,7 @@
       <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="9" t="n">
         <v>20140901</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -2705,7 +2812,7 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="9" t="n">
         <v>20140501</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -2729,7 +2836,7 @@
       <c r="H3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="9" t="n">
         <v>20130801</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2753,7 +2860,7 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="n">
+      <c r="A5" s="9" t="n">
         <v>20130501</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2868,26 +2975,26 @@
         <v>560</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="n">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
         <v>20240604</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>563</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>564</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="8" t="s">
         <v>565</v>
       </c>
     </row>
@@ -2908,7 +3015,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2938,136 +3045,137 @@
       <c r="I1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="8" t="n">
         <v>151</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="7" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="8" t="n">
         <v>2021</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="8" t="n">
         <v>251</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="7" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="8" t="n">
         <v>850</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>569</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="7" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>2020</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" s="8" t="n">
         <v>349</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="7" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="8" t="n">
         <v>351</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>548</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="E6" s="14" t="b">
+      <c r="E6" s="7" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="8" t="s">
         <v>572</v>
       </c>
     </row>
@@ -3088,9 +3196,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H1048576"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="20.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="20.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3627,164 +3735,187 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>622</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="E24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="E24" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="D26" s="9" t="n">
+      <c r="C26" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="8" t="s">
         <v>623</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="s">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="C27" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="D27" s="9" t="n">
+      <c r="C27" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D27" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="8" t="s">
         <v>629</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="8" t="s">
         <v>623</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="D28" s="9" t="n">
+      <c r="C28" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D28" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="8" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="s">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
         <v>579</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>559</v>
-      </c>
-      <c r="D29" s="9" t="n">
+      <c r="C29" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="8" t="s">
         <v>631</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>632</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="D30" s="0" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>2026</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>624</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>633</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3805,20 +3936,20 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>322</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -3826,16 +3957,16 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>45007</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>638</v>
+      <c r="D2" s="8" t="s">
+        <v>639</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>12</v>
@@ -3843,15 +3974,15 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="13" t="n">
         <v>44774</v>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="13" t="n">
         <v>45047</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -3860,16 +3991,16 @@
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="13" t="n">
         <v>44774</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>641</v>
+      <c r="D4" s="13" t="s">
+        <v>642</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -3877,15 +4008,15 @@
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="14" t="n">
         <v>44835</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="13" t="n">
         <v>45047</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -3894,32 +4025,32 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="13" t="n">
         <v>44409</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>638</v>
+      <c r="D6" s="8" t="s">
+        <v>639</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="B7" s="9" t="s">
+      <c r="A7" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="E7" s="9" t="s">
+      <c r="C7" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3940,7 +4071,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -3959,10 +4090,10 @@
         <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>144</v>
@@ -3970,9 +4101,9 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B2" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B2" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -3983,20 +4114,20 @@
         <v>2019</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>208</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B3" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B3" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4007,20 +4138,20 @@
         <v>2021</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B4" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B4" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4031,23 +4162,23 @@
         <v>2019</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B5" s="6" t="b">
+      <c r="B5" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4058,23 +4189,23 @@
         <v>2020</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B6" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B6" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4085,17 +4216,17 @@
         <v>2026</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B7" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B7" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4106,20 +4237,20 @@
         <v>2022</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>208</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B8" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B8" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4130,17 +4261,17 @@
         <v>2020</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B9" s="6" t="b">
+      <c r="B9" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4154,17 +4285,17 @@
         <v>560</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B10" s="6" t="b">
+        <v>667</v>
+      </c>
+      <c r="B10" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4175,20 +4306,20 @@
         <v>2020</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B11" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B11" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4199,17 +4330,17 @@
         <v>2024</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B12" s="6" t="b">
+        <v>667</v>
+      </c>
+      <c r="B12" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4220,23 +4351,23 @@
         <v>2025</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B13" s="6" t="b">
+        <v>667</v>
+      </c>
+      <c r="B13" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4247,20 +4378,20 @@
         <v>2022</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B14" s="6" t="b">
+      <c r="B14" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4271,17 +4402,17 @@
         <v>2022</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B15" s="6" t="b">
+        <v>667</v>
+      </c>
+      <c r="B15" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4292,17 +4423,17 @@
         <v>2021</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B16" s="6" t="b">
+        <v>667</v>
+      </c>
+      <c r="B16" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4313,20 +4444,20 @@
         <v>2021</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B17" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B17" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4337,20 +4468,20 @@
         <v>2023</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>208</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B18" s="6" t="b">
+        <v>667</v>
+      </c>
+      <c r="B18" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4361,20 +4492,20 @@
         <v>2026</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B19" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B19" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4385,20 +4516,20 @@
         <v>2025</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B20" s="6" t="b">
+        <v>649</v>
+      </c>
+      <c r="B20" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4409,20 +4540,20 @@
         <v>2024</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>208</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B21" s="6" t="b">
+        <v>667</v>
+      </c>
+      <c r="B21" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4433,20 +4564,20 @@
         <v>2024</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="B22" s="6" t="b">
+        <v>667</v>
+      </c>
+      <c r="B22" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4456,44 +4587,44 @@
       <c r="D22" s="1" t="n">
         <v>2026</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>651</v>
+      <c r="E22" s="8" t="s">
+        <v>652</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="H22" s="9" t="s">
         <v>689</v>
       </c>
+      <c r="H22" s="8" t="s">
+        <v>690</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>648</v>
-      </c>
-      <c r="B23" s="8" t="n">
+      <c r="A23" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="B23" s="7" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>560</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="G23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>692</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -4513,198 +4644,198 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>693</v>
+      <c r="B1" s="8" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>670</v>
+      <c r="B2" s="8" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="8" t="n">
         <v>2019</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>661</v>
+      <c r="B3" s="8" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="8" t="n">
         <v>2020</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>694</v>
+      <c r="B4" s="8" t="s">
+        <v>695</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="8" t="n">
         <v>2020</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>695</v>
+      <c r="B5" s="8" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="8" t="n">
         <v>2020</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>696</v>
+      <c r="B6" s="8" t="s">
+        <v>697</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="8" t="n">
         <v>2021</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>697</v>
+      <c r="B7" s="8" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="8" t="n">
         <v>2021</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="9" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="n">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="n">
+      <c r="B16" s="8" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="n">
+      <c r="B17" s="8" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="9" t="n">
+      <c r="B18" s="8" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>670</v>
+      <c r="B19" s="8" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>697</v>
+      <c r="B20" s="8" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>702</v>
-      </c>
-    </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>704</v>
+      <c r="B24" s="8" t="s">
+        <v>705</v>
       </c>
     </row>
   </sheetData>
@@ -4724,33 +4855,33 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>144</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="b">
+      <c r="A2" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4761,14 +4892,14 @@
         <v>2023</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="b">
+      <c r="A3" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4779,14 +4910,14 @@
         <v>2023</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="b">
+      <c r="A4" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -4797,14 +4928,14 @@
         <v>2022</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="b">
+      <c r="A5" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4815,11 +4946,11 @@
         <v>2020</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="b">
+      <c r="A6" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4830,10 +4961,10 @@
         <v>2020</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
   </sheetData>
@@ -4853,9 +4984,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L1048576"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="59.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="25.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="25.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="28.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="59.94"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4866,10 +5000,10 @@
         <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>144</v>
@@ -4878,25 +5012,25 @@
         <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="b">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>2025</v>
@@ -4905,13 +5039,13 @@
         <v>2025</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -4919,13 +5053,13 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="b">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>2025</v>
@@ -4934,13 +5068,13 @@
         <v>2026</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -4948,13 +5082,13 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>2025</v>
@@ -4963,13 +5097,13 @@
         <v>2026</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -4977,13 +5111,13 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>2024</v>
@@ -4992,10 +5126,10 @@
         <v>2025</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>729</v>
@@ -5006,22 +5140,22 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="b">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="C6" s="11" t="n">
+        <v>720</v>
+      </c>
+      <c r="C6" s="9" t="n">
         <v>2023</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="9" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>730</v>
@@ -5035,21 +5169,21 @@
       <c r="L6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="b">
+      <c r="A7" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="C7" s="11" t="n">
+        <v>720</v>
+      </c>
+      <c r="C7" s="9" t="n">
         <v>2022</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="9" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>732</v>
@@ -5063,21 +5197,21 @@
       <c r="L7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="b">
+      <c r="A8" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="C8" s="11" t="n">
+        <v>720</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>2022</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="9" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>734</v>
@@ -5091,21 +5225,21 @@
       <c r="L8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="b">
+      <c r="A9" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="C9" s="11" t="n">
+        <v>720</v>
+      </c>
+      <c r="C9" s="9" t="n">
         <v>2022</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="9" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>736</v>
@@ -5119,21 +5253,21 @@
       <c r="L9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="b">
+      <c r="A10" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="C10" s="11" t="n">
+        <v>720</v>
+      </c>
+      <c r="C10" s="9" t="n">
         <v>2021</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="9" t="n">
         <v>2021</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>736</v>
@@ -5147,18 +5281,18 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="b">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="9" t="n">
         <v>2021</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="9" t="n">
         <v>2021</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -5177,17 +5311,17 @@
       <c r="L11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="b">
+      <c r="A12" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="9" t="n">
         <v>2021</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="9" t="n">
         <v>2021</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -5205,18 +5339,18 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="b">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="9" t="n">
         <v>2020</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="9" t="n">
         <v>2020</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -5369,7 +5503,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -5454,7 +5588,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AE12"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="4" style="5" width="12.63"/>
   </cols>
@@ -5513,14 +5647,14 @@
       <c r="AE1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="b">
+      <c r="A2" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="7" t="b">
+      <c r="C2" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5568,14 +5702,14 @@
       <c r="AE2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="b">
+      <c r="A3" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="7" t="b">
+      <c r="C3" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5619,14 +5753,14 @@
       <c r="AE3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="b">
+      <c r="A4" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="7" t="b">
+      <c r="C4" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5674,14 +5808,14 @@
       <c r="AE4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="b">
+      <c r="A5" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="7" t="b">
+      <c r="C5" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5729,14 +5863,14 @@
       <c r="AE5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="b">
+      <c r="A6" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="7" t="b">
+      <c r="C6" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5784,14 +5918,14 @@
       <c r="AE6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="b">
+      <c r="A7" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="7" t="b">
+      <c r="C7" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5839,14 +5973,14 @@
       <c r="AE7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="b">
+      <c r="A8" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="6" t="b">
+      <c r="C8" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5890,14 +6024,14 @@
       <c r="AE8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="b">
+      <c r="A9" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="6" t="b">
+      <c r="C9" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -5921,14 +6055,14 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="b">
+      <c r="A10" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="6" t="b">
+      <c r="C10" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5952,14 +6086,14 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="b">
+      <c r="A11" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="6" t="b">
+      <c r="C11" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -5983,14 +6117,14 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="7" t="n">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6000,13 +6134,13 @@
       <c r="F12" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
         <v>72</v>
       </c>
     </row>
@@ -6027,9 +6161,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="31.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="31.38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6077,7 +6211,7 @@
       <c r="A2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="6" t="b">
+      <c r="B2" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6099,7 +6233,7 @@
       <c r="H2" s="1" t="n">
         <v>299859</v>
       </c>
-      <c r="I2" s="6" t="b">
+      <c r="I2" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6118,7 +6252,7 @@
       <c r="A3" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="6" t="b">
+      <c r="B3" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6140,7 +6274,7 @@
       <c r="H3" s="1" t="n">
         <v>380650</v>
       </c>
-      <c r="I3" s="6" t="b">
+      <c r="I3" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6156,7 +6290,7 @@
       <c r="A4" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="6" t="b">
+      <c r="B4" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6178,7 +6312,7 @@
       <c r="H4" s="1" t="n">
         <v>20000000</v>
       </c>
-      <c r="I4" s="6" t="b">
+      <c r="I4" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6197,7 +6331,7 @@
       <c r="A5" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="6" t="b">
+      <c r="B5" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6219,7 +6353,7 @@
       <c r="H5" s="1" t="n">
         <v>4000000</v>
       </c>
-      <c r="I5" s="6" t="b">
+      <c r="I5" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6240,7 +6374,7 @@
       <c r="A6" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="6" t="b">
+      <c r="B6" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6262,7 +6396,7 @@
       <c r="H6" s="1" t="n">
         <v>300000</v>
       </c>
-      <c r="I6" s="6" t="b">
+      <c r="I6" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6277,7 +6411,7 @@
       <c r="A7" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="6" t="b">
+      <c r="B7" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6299,7 +6433,7 @@
       <c r="H7" s="1" t="n">
         <v>1500000</v>
       </c>
-      <c r="I7" s="6" t="b">
+      <c r="I7" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6317,7 +6451,7 @@
       <c r="A8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="6" t="b">
+      <c r="B8" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6339,7 +6473,7 @@
       <c r="H8" s="1" t="n">
         <v>197699</v>
       </c>
-      <c r="I8" s="6" t="b">
+      <c r="I8" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
@@ -6357,7 +6491,7 @@
       <c r="A9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="6" t="b">
+      <c r="B9" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6379,7 +6513,7 @@
       <c r="H9" s="1" t="n">
         <v>300000</v>
       </c>
-      <c r="I9" s="6" t="b">
+      <c r="I9" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6388,7 +6522,7 @@
       <c r="A10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B10" s="6" t="b">
+      <c r="B10" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6410,7 +6544,7 @@
       <c r="H10" s="1" t="n">
         <v>20000000</v>
       </c>
-      <c r="I10" s="6" t="b">
+      <c r="I10" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6422,7 +6556,7 @@
       <c r="A11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B11" s="6" t="b">
+      <c r="B11" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6444,7 +6578,7 @@
       <c r="H11" s="1" t="n">
         <v>3000000</v>
       </c>
-      <c r="I11" s="6" t="b">
+      <c r="I11" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6453,7 +6587,7 @@
       <c r="A12" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="6" t="b">
+      <c r="B12" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6475,7 +6609,7 @@
       <c r="H12" s="1" t="n">
         <v>281755</v>
       </c>
-      <c r="I12" s="6" t="b">
+      <c r="I12" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6484,7 +6618,7 @@
       <c r="A13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="6" t="b">
+      <c r="B13" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6497,7 +6631,7 @@
       <c r="E13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="6" t="s">
         <v>115</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -6506,16 +6640,16 @@
       <c r="H13" s="1" t="n">
         <v>666485</v>
       </c>
-      <c r="I13" s="6" t="b">
+      <c r="I13" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="6" t="b">
+      <c r="B14" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -6528,7 +6662,7 @@
       <c r="E14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="6" t="s">
         <v>115</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -6537,17 +6671,17 @@
       <c r="H14" s="1" t="n">
         <v>550000</v>
       </c>
-      <c r="I14" s="6" t="b">
+      <c r="I14" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="8" t="n">
         <v>2030</v>
       </c>
     </row>
@@ -6568,7 +6702,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -6633,7 +6767,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -6661,14 +6795,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="b">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="b">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="6" t="b">
+      <c r="C2" s="1" t="b">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D2" s="1" t="n">
@@ -6685,22 +6821,22 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="b">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="7" t="b">
+      <c r="C3" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="9" t="n">
         <v>2021</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="9" t="n">
         <v>2021</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -6709,26 +6845,26 @@
       <c r="G3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="b">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="7" t="b">
+      <c r="C4" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="9" t="n">
         <v>2012</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="9" t="n">
         <v>2012</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -6739,21 +6875,21 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="b">
+      <c r="A5" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C5" s="7" t="b">
+      <c r="C5" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="9" t="n">
         <v>2009</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="9" t="n">
         <v>2011</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -6765,21 +6901,21 @@
       <c r="H5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="b">
+      <c r="A6" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="7" t="b">
+      <c r="C6" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="9" t="n">
         <v>2005</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="9" t="n">
         <v>2009</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -6791,21 +6927,21 @@
       <c r="H6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="b">
+      <c r="A7" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="7" t="b">
+      <c r="C7" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="9" t="n">
         <v>2009</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="9" t="n">
         <v>2009</v>
       </c>
       <c r="F7" s="1" t="s">
@@ -6817,21 +6953,21 @@
       <c r="H7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="b">
+      <c r="A8" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C8" s="7" t="b">
+      <c r="C8" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="9" t="n">
         <v>2009</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="9" t="n">
         <v>2009</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -6843,21 +6979,21 @@
       <c r="H8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="b">
+      <c r="A9" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C9" s="7" t="b">
+      <c r="C9" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="9" t="n">
         <v>2006</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="9" t="n">
         <v>2009</v>
       </c>
       <c r="F9" s="1" t="s">
@@ -6869,21 +7005,21 @@
       <c r="H9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="b">
+      <c r="A10" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="7" t="b">
+      <c r="C10" s="6" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="9" t="n">
         <v>2005</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>2009</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -6895,21 +7031,21 @@
       <c r="H10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="b">
+      <c r="A11" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C11" s="7" t="b">
+      <c r="C11" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="9" t="n">
         <v>2005</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="9" t="n">
         <v>2005</v>
       </c>
       <c r="F11" s="1" t="s">
@@ -6921,21 +7057,21 @@
       <c r="H11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="b">
+      <c r="A12" s="1" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C12" s="7" t="b">
+      <c r="C12" s="6" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="9" t="n">
         <v>2005</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="9" t="n">
         <v>2005</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -6998,9 +7134,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>143</v>
       </c>
@@ -7020,7 +7156,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>148</v>
       </c>
@@ -7038,7 +7174,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>152</v>
       </c>
@@ -7056,7 +7192,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>156</v>
       </c>
@@ -7066,14 +7202,14 @@
       <c r="C4" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>160</v>
       </c>
@@ -7083,14 +7219,14 @@
       <c r="C5" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>164</v>
       </c>
@@ -7106,11 +7242,11 @@
       <c r="E6" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>168</v>
       </c>
@@ -7120,14 +7256,14 @@
       <c r="C7" s="1" t="n">
         <v>2019</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>172</v>
       </c>
@@ -7137,14 +7273,14 @@
       <c r="C8" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>176</v>
       </c>
@@ -7154,14 +7290,14 @@
       <c r="C9" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>179</v>
       </c>
@@ -7171,14 +7307,14 @@
       <c r="C10" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="10" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>182</v>
       </c>
@@ -7194,11 +7330,11 @@
       <c r="E11" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="10" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>186</v>
       </c>
@@ -7214,11 +7350,11 @@
       <c r="E12" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="10" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>190</v>
       </c>
@@ -7234,7 +7370,7 @@
       <c r="E13" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="10" t="s">
         <v>193</v>
       </c>
     </row>
@@ -7267,50 +7403,50 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L52"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="15.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="9" width="14.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="19.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="9" width="15.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="15.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="14.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="8" width="15.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>202</v>
       </c>
     </row>
@@ -7318,28 +7454,28 @@
       <c r="A2" s="5" t="n">
         <v>41493</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>210</v>
       </c>
     </row>
@@ -7347,31 +7483,31 @@
       <c r="A3" s="5" t="n">
         <v>41789</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>217</v>
       </c>
     </row>
@@ -7379,34 +7515,34 @@
       <c r="A4" s="5" t="n">
         <v>41855</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="8" t="s">
         <v>223</v>
       </c>
     </row>
@@ -7414,37 +7550,37 @@
       <c r="A5" s="5" t="n">
         <v>41855</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="K5" s="9" t="s">
+      <c r="K5" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>229</v>
       </c>
     </row>
@@ -7452,37 +7588,37 @@
       <c r="A6" s="5" t="n">
         <v>42226</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>235</v>
       </c>
     </row>
@@ -7490,28 +7626,28 @@
       <c r="A7" s="5" t="n">
         <v>42226</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="8" t="s">
         <v>240</v>
       </c>
     </row>
@@ -7519,37 +7655,37 @@
       <c r="A8" s="5" t="n">
         <v>42583</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>245</v>
       </c>
     </row>
@@ -7557,31 +7693,31 @@
       <c r="A9" s="5" t="n">
         <v>42949</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="8" t="s">
         <v>249</v>
       </c>
     </row>
@@ -7589,34 +7725,34 @@
       <c r="A10" s="5" t="n">
         <v>43237</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>253</v>
       </c>
     </row>
@@ -7624,37 +7760,37 @@
       <c r="A11" s="5" t="n">
         <v>43313</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="8" t="s">
         <v>259</v>
       </c>
     </row>
@@ -7662,37 +7798,37 @@
       <c r="A12" s="5" t="n">
         <v>43677</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>265</v>
       </c>
     </row>
@@ -7700,34 +7836,34 @@
       <c r="A13" s="5" t="n">
         <v>43842</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>272</v>
       </c>
     </row>
@@ -7735,34 +7871,34 @@
       <c r="A14" s="5" t="n">
         <v>43872</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="8" t="s">
         <v>279</v>
       </c>
     </row>
@@ -7770,34 +7906,34 @@
       <c r="A15" s="5" t="n">
         <v>43901</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="8" t="s">
         <v>285</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="K15" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="8" t="s">
         <v>287</v>
       </c>
     </row>
@@ -7805,37 +7941,37 @@
       <c r="A16" s="5" t="n">
         <v>44041</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="K16" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="L16" s="8" t="s">
         <v>295</v>
       </c>
     </row>
@@ -7843,34 +7979,34 @@
       <c r="A17" s="5" t="n">
         <v>44223</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="8" t="s">
         <v>301</v>
       </c>
     </row>
@@ -7878,31 +8014,31 @@
       <c r="A18" s="5" t="n">
         <v>44232</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="8" t="s">
         <v>306</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="8" t="s">
         <v>307</v>
       </c>
     </row>
@@ -7910,34 +8046,34 @@
       <c r="A19" s="5" t="n">
         <v>44271</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="K19" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="L19" s="8" t="s">
         <v>312</v>
       </c>
     </row>
@@ -7945,37 +8081,37 @@
       <c r="A20" s="5" t="n">
         <v>44285</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="8" t="s">
         <v>319</v>
       </c>
     </row>
@@ -7983,37 +8119,37 @@
       <c r="A21" s="5" t="n">
         <v>44295</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="K21" s="8" t="s">
         <v>326</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="8" t="s">
         <v>327</v>
       </c>
     </row>
@@ -8021,37 +8157,37 @@
       <c r="A22" s="5" t="n">
         <v>44363</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="8" t="s">
         <v>330</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="8" t="s">
         <v>336</v>
       </c>
     </row>
@@ -8059,31 +8195,31 @@
       <c r="A23" s="5" t="n">
         <v>44399</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="K23" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="8" t="s">
         <v>340</v>
       </c>
     </row>
@@ -8091,37 +8227,37 @@
       <c r="A24" s="5" t="n">
         <v>44417</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="I24" s="9" t="s">
+      <c r="I24" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="L24" s="8" t="s">
         <v>346</v>
       </c>
     </row>
@@ -8129,37 +8265,37 @@
       <c r="A25" s="5" t="n">
         <v>44600</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="I25" s="9" t="s">
+      <c r="I25" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="J25" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="K25" s="9" t="s">
+      <c r="K25" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="L25" s="8" t="s">
         <v>349</v>
       </c>
     </row>
@@ -8167,31 +8303,31 @@
       <c r="A26" s="5" t="n">
         <v>44644</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="L26" s="8" t="s">
         <v>356</v>
       </c>
     </row>
@@ -8199,37 +8335,37 @@
       <c r="A27" s="5" t="n">
         <v>44659</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="8" t="s">
         <v>358</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="I27" s="9" t="s">
+      <c r="I27" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="K27" s="9" t="s">
+      <c r="K27" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="L27" s="8" t="s">
         <v>362</v>
       </c>
     </row>
@@ -8237,28 +8373,28 @@
       <c r="A28" s="5" t="n">
         <v>44775</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="C28" s="8" t="s">
         <v>363</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="I28" s="9" t="s">
+      <c r="I28" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="8" t="s">
         <v>367</v>
       </c>
     </row>
@@ -8266,34 +8402,34 @@
       <c r="A29" s="5" t="n">
         <v>44776</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="K29" s="9" t="s">
+      <c r="K29" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="L29" s="9" t="s">
+      <c r="L29" s="8" t="s">
         <v>371</v>
       </c>
     </row>
@@ -8301,37 +8437,37 @@
       <c r="A30" s="5" t="n">
         <v>44826</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="C30" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="8" t="s">
         <v>375</v>
       </c>
-      <c r="K30" s="9" t="s">
+      <c r="K30" s="8" t="s">
         <v>376</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="L30" s="8" t="s">
         <v>377</v>
       </c>
     </row>
@@ -8339,37 +8475,37 @@
       <c r="A31" s="5" t="n">
         <v>44839</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="8" t="s">
         <v>378</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E31" s="9" t="s">
+      <c r="E31" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F31" s="9" t="s">
+      <c r="F31" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="8" t="s">
         <v>380</v>
       </c>
-      <c r="K31" s="9" t="s">
+      <c r="K31" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="L31" s="8" t="s">
         <v>382</v>
       </c>
     </row>
@@ -8377,37 +8513,37 @@
       <c r="A32" s="5" t="n">
         <v>44972</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="D32" s="9" t="s">
+      <c r="D32" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="8" t="s">
         <v>383</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="8" t="s">
         <v>384</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="I32" s="9" t="s">
+      <c r="I32" s="8" t="s">
         <v>385</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="K32" s="9" t="s">
+      <c r="K32" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="L32" s="8" t="s">
         <v>387</v>
       </c>
     </row>
@@ -8415,34 +8551,34 @@
       <c r="A33" s="5" t="n">
         <v>45012</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="8" t="s">
         <v>388</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E33" s="9" t="s">
+      <c r="E33" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F33" s="9" t="s">
+      <c r="F33" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="J33" s="8" t="s">
         <v>390</v>
       </c>
-      <c r="K33" s="9" t="s">
+      <c r="K33" s="8" t="s">
         <v>391</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="L33" s="8" t="s">
         <v>392</v>
       </c>
     </row>
@@ -8450,34 +8586,34 @@
       <c r="A34" s="5" t="n">
         <v>45146</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="D34" s="9" t="s">
+      <c r="D34" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G34" s="9" t="s">
+      <c r="G34" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="J34" s="9" t="s">
+      <c r="J34" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="K34" s="9" t="s">
+      <c r="K34" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="L34" s="9" t="s">
+      <c r="L34" s="8" t="s">
         <v>396</v>
       </c>
     </row>
@@ -8485,37 +8621,37 @@
       <c r="A35" s="5" t="n">
         <v>45211</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="8" t="s">
         <v>397</v>
       </c>
-      <c r="D35" s="9" t="s">
+      <c r="D35" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E35" s="9" t="s">
+      <c r="E35" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="G35" s="9" t="s">
+      <c r="G35" s="8" t="s">
         <v>399</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H35" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="8" t="s">
         <v>400</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="J35" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="K35" s="9" t="s">
+      <c r="K35" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="L35" s="8" t="s">
         <v>403</v>
       </c>
     </row>
@@ -8523,34 +8659,34 @@
       <c r="A36" s="5" t="n">
         <v>45239</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I36" s="8" t="s">
         <v>408</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="K36" s="9" t="s">
+      <c r="K36" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="L36" s="9" t="s">
+      <c r="L36" s="8" t="s">
         <v>411</v>
       </c>
     </row>
@@ -8558,37 +8694,37 @@
       <c r="A37" s="5" t="n">
         <v>45266</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="E37" s="9" t="s">
+      <c r="E37" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F37" s="9" t="s">
+      <c r="F37" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="8" t="s">
         <v>416</v>
       </c>
-      <c r="I37" s="9" t="s">
+      <c r="I37" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="J37" s="9" t="s">
+      <c r="J37" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="K37" s="9" t="s">
+      <c r="K37" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="L37" s="9" t="s">
+      <c r="L37" s="8" t="s">
         <v>420</v>
       </c>
     </row>
@@ -8596,31 +8732,31 @@
       <c r="A38" s="5" t="n">
         <v>45274</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F38" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="8" t="s">
         <v>422</v>
       </c>
-      <c r="J38" s="9" t="s">
+      <c r="J38" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="K38" s="9" t="s">
+      <c r="K38" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="L38" s="9" t="s">
+      <c r="L38" s="8" t="s">
         <v>425</v>
       </c>
     </row>
@@ -8628,31 +8764,31 @@
       <c r="A39" s="5" t="n">
         <v>45300</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F39" s="9" t="s">
+      <c r="F39" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="I39" s="9" t="s">
+      <c r="I39" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="J39" s="9" t="s">
+      <c r="J39" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="K39" s="9" t="s">
+      <c r="K39" s="8" t="s">
         <v>431</v>
       </c>
     </row>
@@ -8660,37 +8796,37 @@
       <c r="A40" s="5" t="n">
         <v>45330</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="F40" s="9" t="s">
+      <c r="F40" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I40" s="9" t="s">
+      <c r="I40" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="J40" s="9" t="s">
+      <c r="J40" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="K40" s="9" t="s">
+      <c r="K40" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="L40" s="9" t="s">
+      <c r="L40" s="8" t="s">
         <v>436</v>
       </c>
     </row>
@@ -8698,37 +8834,37 @@
       <c r="A41" s="5" t="n">
         <v>45337</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" s="8" t="s">
         <v>437</v>
       </c>
-      <c r="D41" s="9" t="s">
+      <c r="D41" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="F41" s="9" t="s">
+      <c r="F41" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I41" s="13" t="s">
+      <c r="I41" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="J41" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="K41" s="9" t="s">
+      <c r="K41" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="L41" s="9" t="s">
+      <c r="L41" s="8" t="s">
         <v>441</v>
       </c>
     </row>
@@ -8736,37 +8872,37 @@
       <c r="A42" s="5" t="n">
         <v>45358</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="F42" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I42" s="9" t="s">
+      <c r="I42" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="J42" s="9" t="s">
+      <c r="J42" s="8" t="s">
         <v>444</v>
       </c>
-      <c r="K42" s="9" t="s">
+      <c r="K42" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="L42" s="9" t="s">
+      <c r="L42" s="8" t="s">
         <v>445</v>
       </c>
     </row>
@@ -8774,28 +8910,28 @@
       <c r="A43" s="5" t="n">
         <v>45380</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="C43" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="D43" s="9" t="s">
+      <c r="D43" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F43" s="9" t="s">
+      <c r="F43" s="8" t="s">
         <v>447</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H43" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="I43" s="9" t="s">
+      <c r="I43" s="8" t="s">
         <v>450</v>
       </c>
     </row>
@@ -8803,37 +8939,37 @@
       <c r="A44" s="5" t="n">
         <v>45469</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C44" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D44" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F44" s="9" t="s">
+      <c r="F44" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G44" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="I44" s="9" t="s">
+      <c r="I44" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="J44" s="9" t="s">
+      <c r="J44" s="8" t="s">
         <v>454</v>
       </c>
-      <c r="K44" s="9" t="s">
+      <c r="K44" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="L44" s="9" t="s">
+      <c r="L44" s="8" t="s">
         <v>456</v>
       </c>
     </row>
@@ -8841,34 +8977,34 @@
       <c r="A45" s="5" t="n">
         <v>45474</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C45" s="9" t="s">
+      <c r="C45" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="D45" s="9" t="s">
+      <c r="D45" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E45" s="9" t="s">
+      <c r="E45" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F45" s="9" t="s">
+      <c r="F45" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="I45" s="9" t="s">
+      <c r="I45" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="J45" s="9" t="s">
+      <c r="J45" s="8" t="s">
         <v>461</v>
       </c>
-      <c r="K45" s="9" t="s">
+      <c r="K45" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="L45" s="9" t="s">
+      <c r="L45" s="8" t="s">
         <v>463</v>
       </c>
     </row>
@@ -8876,37 +9012,37 @@
       <c r="A46" s="5" t="n">
         <v>45511</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C46" s="9" t="s">
+      <c r="C46" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="D46" s="9" t="s">
+      <c r="D46" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F46" s="9" t="s">
+      <c r="F46" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="I46" s="9" t="s">
+      <c r="I46" s="8" t="s">
         <v>467</v>
       </c>
-      <c r="J46" s="9" t="s">
+      <c r="J46" s="8" t="s">
         <v>468</v>
       </c>
-      <c r="K46" s="9" t="s">
+      <c r="K46" s="8" t="s">
         <v>469</v>
       </c>
-      <c r="L46" s="9" t="s">
+      <c r="L46" s="8" t="s">
         <v>470</v>
       </c>
     </row>
@@ -8914,34 +9050,34 @@
       <c r="A47" s="5" t="n">
         <v>45598</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C47" s="9" t="s">
+      <c r="C47" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E47" s="9" t="s">
+      <c r="E47" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="F47" s="9" t="s">
+      <c r="F47" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="H47" s="9" t="s">
+      <c r="H47" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I47" s="9" t="s">
+      <c r="I47" s="8" t="s">
         <v>473</v>
       </c>
-      <c r="J47" s="9" t="s">
+      <c r="J47" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="K47" s="9" t="s">
+      <c r="K47" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="L47" s="9" t="s">
+      <c r="L47" s="8" t="s">
         <v>476</v>
       </c>
     </row>
@@ -8949,34 +9085,34 @@
       <c r="A48" s="5" t="n">
         <v>45609</v>
       </c>
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C48" s="9" t="s">
+      <c r="C48" s="8" t="s">
         <v>477</v>
       </c>
-      <c r="D48" s="9" t="s">
+      <c r="D48" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F48" s="13" t="s">
+      <c r="F48" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="H48" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="I48" s="9" t="s">
+      <c r="I48" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="J48" s="8" t="s">
         <v>480</v>
       </c>
-      <c r="K48" s="9" t="s">
+      <c r="K48" s="8" t="s">
         <v>455</v>
       </c>
-      <c r="L48" s="9" t="s">
+      <c r="L48" s="8" t="s">
         <v>481</v>
       </c>
     </row>
@@ -8984,34 +9120,34 @@
       <c r="A49" s="5" t="n">
         <v>45742</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="F49" s="8" t="s">
         <v>483</v>
       </c>
-      <c r="H49" s="9" t="s">
+      <c r="H49" s="8" t="s">
         <v>484</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="I49" s="8" t="s">
         <v>485</v>
       </c>
-      <c r="J49" s="9" t="s">
+      <c r="J49" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="K49" s="9" t="s">
+      <c r="K49" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="L49" s="9" t="s">
+      <c r="L49" s="8" t="s">
         <v>488</v>
       </c>
     </row>
@@ -9019,37 +9155,37 @@
       <c r="A50" s="5" t="n">
         <v>45873</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="B50" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="D50" s="9" t="s">
+      <c r="D50" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="F50" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="G50" s="9" t="s">
+      <c r="G50" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="I50" s="9" t="s">
+      <c r="I50" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="J50" s="9" t="s">
+      <c r="J50" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="K50" s="9" t="s">
+      <c r="K50" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="L50" s="9" t="s">
+      <c r="L50" s="8" t="s">
         <v>494</v>
       </c>
     </row>
@@ -9057,72 +9193,72 @@
       <c r="A51" s="5" t="n">
         <v>45878</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="8" t="s">
         <v>495</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="E51" s="9" t="s">
+      <c r="E51" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="F51" s="9" t="s">
+      <c r="F51" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="H51" s="9" t="s">
+      <c r="H51" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="I51" s="9" t="s">
+      <c r="I51" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="J51" s="9" t="s">
+      <c r="J51" s="8" t="s">
         <v>499</v>
       </c>
-      <c r="K51" s="9" t="s">
+      <c r="K51" s="8" t="s">
         <v>500</v>
       </c>
-      <c r="L51" s="9" t="s">
+      <c r="L51" s="8" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="101.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="1603.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="n">
         <v>45967</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B52" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="C52" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D52" s="8" t="s">
         <v>503</v>
       </c>
-      <c r="E52" s="9" t="s">
+      <c r="E52" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="F52" s="9" t="s">
+      <c r="F52" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="G52" s="9" t="s">
+      <c r="G52" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="H52" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="I52" s="13" t="s">
+      <c r="I52" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="J52" s="9" t="s">
+      <c r="J52" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="K52" s="9" t="s">
+      <c r="K52" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="L52" s="9" t="s">
+      <c r="L52" s="8" t="s">
         <v>509</v>
       </c>
     </row>
@@ -9148,11 +9284,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="9" width="25.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="48.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="25.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="48.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9216,7 +9352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2020</v>
       </c>
@@ -9238,7 +9374,7 @@
       <c r="G3" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>528</v>
       </c>
       <c r="I3" s="1" t="n">
@@ -9248,7 +9384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>2020</v>
       </c>
@@ -9277,7 +9413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>2021</v>
       </c>
@@ -9299,7 +9435,7 @@
       <c r="G5" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>528</v>
       </c>
       <c r="I5" s="1" t="n">
@@ -9309,7 +9445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>2021</v>
       </c>
@@ -9338,7 +9474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>2022</v>
       </c>
@@ -9360,7 +9496,7 @@
       <c r="G7" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="10" t="s">
         <v>528</v>
       </c>
       <c r="I7" s="1" t="n">
@@ -9370,7 +9506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>2022</v>
       </c>
@@ -9399,7 +9535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>2022</v>
       </c>
@@ -9428,7 +9564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>2022</v>
       </c>
@@ -9450,7 +9586,7 @@
       <c r="G10" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="10" t="s">
         <v>538</v>
       </c>
       <c r="I10" s="1" t="n">
@@ -9460,7 +9596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>2022</v>
       </c>
@@ -9489,7 +9625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>2023</v>
       </c>
@@ -9511,7 +9647,7 @@
       <c r="G12" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="10" t="s">
         <v>538</v>
       </c>
       <c r="I12" s="1" t="n">
@@ -9521,7 +9657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>2023</v>
       </c>
@@ -9543,7 +9679,7 @@
       <c r="G13" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="10" t="s">
         <v>541</v>
       </c>
       <c r="I13" s="1" t="n">
@@ -9553,7 +9689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>2023</v>
       </c>
@@ -9575,7 +9711,7 @@
       <c r="G14" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="10" t="s">
         <v>528</v>
       </c>
       <c r="I14" s="1" t="n">
@@ -9585,7 +9721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>2023</v>
       </c>
@@ -9607,7 +9743,7 @@
       <c r="G15" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="10" t="s">
         <v>542</v>
       </c>
       <c r="I15" s="1" t="n">
@@ -9617,7 +9753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>2023</v>
       </c>
@@ -9639,14 +9775,14 @@
       <c r="G16" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="8" t="n">
         <v>4.45</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" s="8" t="n">
         <v>4.5</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>2024</v>
       </c>
@@ -9668,17 +9804,17 @@
       <c r="G17" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="10" t="s">
         <v>538</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="8" t="n">
         <v>4.5</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="8" t="n">
         <v>4.625</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>2024</v>
       </c>
@@ -9700,27 +9836,27 @@
       <c r="G18" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="10" t="s">
         <v>541</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="8" t="n">
         <v>4.6875</v>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="J18" s="8" t="n">
         <v>4.75</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="n">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D19" s="8" t="n">
         <v>892</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -9732,180 +9868,180 @@
       <c r="G19" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="10" t="s">
         <v>542</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="9" t="n">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="8" t="s">
         <v>544</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>992</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="8" t="s">
         <v>545</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="8" t="n">
         <v>4.82</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="J20" s="8" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="9" t="n">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D21" s="9" t="n">
+      <c r="D21" s="8" t="n">
         <v>349</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>546</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="J21" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="9" t="n">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>151</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="8" t="s">
         <v>537</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="8" t="n">
         <v>3.903</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J22" s="8" t="n">
         <v>3.815</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="n">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>351</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>548</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="8" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="n">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>850</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="8" t="s">
         <v>525</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="8" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="n">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>349</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>546</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="8" t="s">
         <v>547</v>
       </c>
     </row>

--- a/CV.xlsx
+++ b/CV.xlsx
@@ -3702,7 +3702,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>0</v>
+        <v>2026</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>614</v>

--- a/CV.xlsx
+++ b/CV.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="749">
   <si>
     <t xml:space="preserve">degree</t>
   </si>
@@ -1920,6 +1920,12 @@
     <t xml:space="preserve">Harriet Mason</t>
   </si>
   <si>
+    <t xml:space="preserve">Visualising Uncertainty for Exploratory Data Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co-advised with Dianne Cook and Sarah Goodwin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Economics</t>
   </si>
   <si>
@@ -1941,7 +1947,7 @@
     <t xml:space="preserve">UNL Undergraduate Research Program</t>
   </si>
   <si>
-    <t xml:space="preserve">Transferred to Southern Illinois University due to program elimination at UNL</t>
+    <t xml:space="preserve">Transferred to Southern Illinois University due to program elimination</t>
   </si>
   <si>
     <t xml:space="preserve">Student Name</t>
@@ -3796,13 +3802,19 @@
       <c r="F25" s="8" t="s">
         <v>625</v>
       </c>
+      <c r="G25" s="0" t="s">
+        <v>626</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
         <v>579</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>283</v>
@@ -3814,7 +3826,7 @@
         <v>2025</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>623</v>
@@ -3828,7 +3840,7 @@
         <v>579</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>283</v>
@@ -3840,7 +3852,7 @@
         <v>2025</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>623</v>
@@ -3866,7 +3878,7 @@
         <v>2026</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3874,7 +3886,7 @@
         <v>579</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>283</v>
@@ -3886,13 +3898,13 @@
         <v>2026</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3914,8 +3926,11 @@
       <c r="F30" s="0" t="s">
         <v>624</v>
       </c>
+      <c r="G30" s="0" t="s">
+        <v>393</v>
+      </c>
       <c r="H30" s="0" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -3940,16 +3955,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>322</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>18</v>
@@ -3957,16 +3972,16 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>45007</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>12</v>
@@ -3974,7 +3989,7 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>14</v>
@@ -3991,7 +4006,7 @@
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>14</v>
@@ -4000,7 +4015,7 @@
         <v>44774</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
@@ -4008,7 +4023,7 @@
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -4025,7 +4040,7 @@
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
@@ -4034,7 +4049,7 @@
         <v>44409</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -4042,13 +4057,13 @@
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>16</v>
@@ -4090,10 +4105,10 @@
         <v>36</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>144</v>
@@ -4101,7 +4116,7 @@
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B2" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4114,18 +4129,18 @@
         <v>2019</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>208</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B3" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4138,18 +4153,18 @@
         <v>2021</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>653</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B4" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -4162,16 +4177,16 @@
         <v>2019</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4189,21 +4204,21 @@
         <v>2020</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B6" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4216,15 +4231,15 @@
         <v>2026</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B7" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4237,18 +4252,18 @@
         <v>2022</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>208</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B8" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4261,10 +4276,10 @@
         <v>2020</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4285,15 +4300,15 @@
         <v>560</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B10" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -4306,18 +4321,18 @@
         <v>2020</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B11" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4330,15 +4345,15 @@
         <v>2024</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B12" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4351,21 +4366,21 @@
         <v>2025</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B13" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4378,13 +4393,13 @@
         <v>2022</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4402,15 +4417,15 @@
         <v>2022</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B15" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -4423,15 +4438,15 @@
         <v>2021</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B16" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -4444,18 +4459,18 @@
         <v>2021</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B17" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4468,18 +4483,18 @@
         <v>2023</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>208</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B18" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4492,18 +4507,18 @@
         <v>2026</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B19" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4516,18 +4531,18 @@
         <v>2025</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B20" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4540,18 +4555,18 @@
         <v>2024</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>208</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B21" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4564,18 +4579,18 @@
         <v>2024</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B22" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4588,21 +4603,21 @@
         <v>2026</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">TRUE()</f>
@@ -4618,13 +4633,13 @@
         <v>560</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
     </row>
   </sheetData>
@@ -4651,7 +4666,7 @@
         <v>510</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4659,7 +4674,7 @@
         <v>2022</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4667,7 +4682,7 @@
         <v>2019</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4675,7 +4690,7 @@
         <v>2020</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4683,7 +4698,7 @@
         <v>2020</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4691,7 +4706,7 @@
         <v>2020</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4699,7 +4714,7 @@
         <v>2021</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4707,7 +4722,7 @@
         <v>2021</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4715,7 +4730,7 @@
         <v>2021</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4723,7 +4738,7 @@
         <v>2022</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4731,7 +4746,7 @@
         <v>2020</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4739,7 +4754,7 @@
         <v>2021</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4747,7 +4762,7 @@
         <v>2022</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4755,7 +4770,7 @@
         <v>2023</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4763,7 +4778,7 @@
         <v>2022</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4771,7 +4786,7 @@
         <v>2023</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4779,7 +4794,7 @@
         <v>2023</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4787,7 +4802,7 @@
         <v>2023</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4795,7 +4810,7 @@
         <v>2023</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4803,7 +4818,7 @@
         <v>2025</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4811,7 +4826,7 @@
         <v>2025</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4819,7 +4834,7 @@
         <v>2025</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4827,7 +4842,7 @@
         <v>2025</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4835,7 +4850,7 @@
         <v>2026</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
     </row>
   </sheetData>
@@ -4862,22 +4877,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>144</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4892,10 +4907,10 @@
         <v>2023</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4910,10 +4925,10 @@
         <v>2023</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4928,10 +4943,10 @@
         <v>2022</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4946,7 +4961,7 @@
         <v>2020</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4961,10 +4976,10 @@
         <v>2020</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -5000,10 +5015,10 @@
         <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>144</v>
@@ -5012,13 +5027,13 @@
         <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -5030,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>2025</v>
@@ -5039,13 +5054,13 @@
         <v>2025</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -5059,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>2025</v>
@@ -5068,13 +5083,13 @@
         <v>2026</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -5088,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>2025</v>
@@ -5097,13 +5112,13 @@
         <v>2026</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -5117,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>2024</v>
@@ -5126,13 +5141,13 @@
         <v>2025</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -5146,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>2023</v>
@@ -5155,13 +5170,13 @@
         <v>2023</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -5174,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>2022</v>
@@ -5183,13 +5198,13 @@
         <v>2022</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -5202,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>2022</v>
@@ -5211,13 +5226,13 @@
         <v>2022</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -5230,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>2022</v>
@@ -5239,13 +5254,13 @@
         <v>2022</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -5258,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>2021</v>
@@ -5267,13 +5282,13 @@
         <v>2021</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -5287,7 +5302,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>2021</v>
@@ -5296,13 +5311,13 @@
         <v>2021</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -5316,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>2021</v>
@@ -5328,10 +5343,10 @@
         <v>352</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -5345,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>2020</v>
@@ -5354,16 +5369,16 @@
         <v>2020</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
